--- a/PCB_Health.V2.xlsx
+++ b/PCB_Health.V2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phdgc\Downloads\upenn-dune-gib\PCB_Health\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44CE28D8-D328-420F-B31B-B890E5EC9F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{818BE190-239F-4D9B-AEDC-0873AD2FEED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5700" yWindow="-18645" windowWidth="45660" windowHeight="16245" xr2:uid="{2BB65666-669A-40E2-864A-7429342188B6}"/>
+    <workbookView xWindow="9405" yWindow="-18000" windowWidth="45660" windowHeight="16245" xr2:uid="{2BB65666-669A-40E2-864A-7429342188B6}"/>
   </bookViews>
   <sheets>
     <sheet name="PCB_Health.V2" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="132">
   <si>
     <t>Reference</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t xml:space="preserve">ESP32-POE-ISO-WROVER </t>
+  </si>
+  <si>
+    <t>MFR-25FTE52-220R</t>
   </si>
 </sst>
 </file>
@@ -1277,6 +1280,7 @@
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="27.7265625" customWidth="1"/>
     <col min="3" max="3" width="18.26953125" customWidth="1"/>
     <col min="5" max="5" width="19.6328125" customWidth="1"/>
     <col min="6" max="6" width="20.453125" customWidth="1"/>
@@ -1830,7 +1834,7 @@
         <v>107</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="K19" t="s">
         <v>54</v>
